--- a/data/trans_dic/IP31KM12_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM12_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,87; 100,0</t>
+          <t>93,72; 99,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,77; 99,44</t>
+          <t>93,39; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95,96; 99,39</t>
+          <t>95,4; 99,39</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,1; 97,34</t>
+          <t>96,92; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96,61; 100,0</t>
+          <t>85,95; 97,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,62; 98,31</t>
+          <t>92,67; 98,52</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,14; 100,0</t>
+          <t>92,28; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,87; 100,0</t>
+          <t>90,64; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,53; 99,66</t>
+          <t>94,87; 99,73</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>83,06; 97,05</t>
+          <t>92,46; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92,83; 100,0</t>
+          <t>84,31; 97,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,23; 98,58</t>
+          <t>90,58; 98,46</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86,86; 98,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,16; 98,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,71; 99,32</t>
+          <t>92,93; 99,21</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>90,38; 98,14</t>
+          <t>98,86; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>98,68; 100,0</t>
+          <t>90,06; 97,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95,87; 99,0</t>
+          <t>95,48; 98,97</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>96,99; 100,0</t>
+          <t>96,2; 100,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>96,35; 100,0</t>
+          <t>97,6; 100,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97,6; 99,82</t>
+          <t>97,86; 99,86</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>95,96; 98,23</t>
+          <t>98,26; 99,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>98,26; 99,56</t>
+          <t>95,71; 97,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>97,49; 98,75</t>
+          <t>97,31; 98,67</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>92</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71400</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>138</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>124079</t>
+          <t>112397</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>123628</t>
+          <t>97747</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>247705</t>
+          <t>210144</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>119206; 125649</t>
+          <t>107732; 114380</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>118551; 125712</t>
+          <t>92765; 99333</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>241877; 250527</t>
+          <t>204418; 212973</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>85</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51622</t>
+          <t>56958</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64214</t>
+          <t>50291</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115837</t>
+          <t>107249</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47830; 54076</t>
+          <t>55535; 57299</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62439; 64633</t>
+          <t>46510; 52840</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111319; 118152</t>
+          <t>103250; 109758</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>91</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>68136</t>
+          <t>68819</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>74365</t>
+          <t>68892</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142501</t>
+          <t>137711</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63510; 69682</t>
+          <t>64425; 69816</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69990; 75367</t>
+          <t>63866; 70462</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>137108; 144555</t>
+          <t>133076; 139901</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31613</t>
+          <t>38993</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40141</t>
+          <t>32745</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71754</t>
+          <t>71739</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>28405; 33192</t>
+          <t>36593; 39579</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37800; 40719</t>
+          <t>29821; 34460</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68350; 73859</t>
+          <t>67888; 73796</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>70</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>41738</t>
+          <t>47209</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>41659</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95520</t>
+          <t>88868</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38470; 43615</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38155; 43650</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91900; 97407</t>
+          <t>85023; 90774</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>167</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>118157</t>
+          <t>140248</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>154654</t>
+          <t>116032</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>272811</t>
+          <t>256281</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>111802; 121391</t>
+          <t>138965; 140571</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>153003; 155044</t>
+          <t>109716; 119169</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>267240; 275961</t>
+          <t>250522; 259684</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>183</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>127941</t>
+          <t>155679</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>152613</t>
+          <t>137256</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>280552</t>
+          <t>292935</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>124796; 128665</t>
+          <t>151170; 157136</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>148528; 154159</t>
+          <t>134592; 137900</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>276026; 282312</t>
+          <t>288712; 294610</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>888</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>634685</t>
+          <t>680565</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>738002</t>
+          <t>599545</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1372687</t>
+          <t>1280109</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>626735; 641562</t>
+          <t>674888; 684044</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>731772; 741486</t>
+          <t>591684; 605462</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1362794; 1380432</t>
+          <t>1269948; 1287702</t>
         </is>
       </c>
     </row>
